--- a/AAII_Financials/Quarterly/GLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GLT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>GLT</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>320400</v>
+      </c>
+      <c r="E8" s="3">
         <v>329900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>357000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>378200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>373900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>371800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>364000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>381700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>334500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>279700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>244900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>225700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>235300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>233500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>216200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>231600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>231000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>232500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>235100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>229100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>229500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>209900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>215700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>211200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>209300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>210100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>380900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>391800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>393000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>406600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>289500</v>
+      </c>
+      <c r="E9" s="3">
         <v>285400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>338900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>342000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>331500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>334400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>326600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>350000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>302900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>241300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>209400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>186400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>194500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>195200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>184100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>194700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>194600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>194500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>197600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>193500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>198800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>180000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>182400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>174600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>171000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>172700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>313000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>671100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>336100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E10" s="3">
         <v>44500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>42400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>37400</v>
       </c>
       <c r="I10" s="3">
         <v>37400</v>
       </c>
       <c r="J10" s="3">
+        <v>37400</v>
+      </c>
+      <c r="K10" s="3">
         <v>31700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>39300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>40800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>32100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>36900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>36400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>37500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>35600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>30700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>29900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>33300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>36600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>38300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>37400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>67900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-279300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>56900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,34 +1298,37 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>17800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>30700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>42500</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>117300</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1326,8 +1345,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E17" s="3">
         <v>327300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>367500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>372100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>396800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>405800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>355000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>497600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>345800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>265100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>236800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>208400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>221500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>219400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>207100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>219300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>217700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>218000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>219900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>217500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>227300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>205500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>208100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>203500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>200000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>199700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>367400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>371100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>422200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>381200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-22900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-34000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-115900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-29200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,233 +1747,240 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-76100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-400</v>
       </c>
       <c r="W20" s="3">
         <v>-400</v>
       </c>
       <c r="X20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y20" s="3">
         <v>2400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E21" s="3">
         <v>16700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>25000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-98700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>30800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>25700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>27200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-50000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>26300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>26500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>24000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>14600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>35100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>36000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>52900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-13400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E22" s="3">
         <v>17400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1700</v>
-      </c>
-      <c r="P22" s="3">
-        <v>1800</v>
       </c>
       <c r="Q22" s="3">
         <v>1800</v>
@@ -1950,7 +1989,7 @@
         <v>1800</v>
       </c>
       <c r="S22" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="T22" s="3">
         <v>1900</v>
@@ -1959,224 +1998,233 @@
         <v>1900</v>
       </c>
       <c r="V22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W22" s="3">
         <v>4700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>3900</v>
       </c>
       <c r="AF22" s="3">
         <v>3900</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-44300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-125100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-64600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>17600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-33400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E24" s="3">
         <v>3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-16900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-19900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-17200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-49100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-108200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-44800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>11600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-49100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-108200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-44800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,91 +2600,94 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E29" s="3">
         <v>-400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-2900</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-600</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>2500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>2600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>3600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-76900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-94500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>3300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>7100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1800</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>76100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>400</v>
       </c>
       <c r="W32" s="3">
         <v>400</v>
       </c>
       <c r="X32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-49500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-108300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-44900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-80100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-95800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-49500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-108300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-44900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-80100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-95800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E41" s="3">
         <v>52700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>53900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>88600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>95300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>80500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>138400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>84200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>87400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>99600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>59200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>104200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>57000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>58900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>76700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>142700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>234100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>107200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>117300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>116200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>84300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>69400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>57200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>55400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>50800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,376 +3625,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>171000</v>
+      </c>
+      <c r="E43" s="3">
         <v>168400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>189600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>196900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>195700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>192400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>209500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>221200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>170200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>149000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>144200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>126500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>122800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>133600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>121700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>128700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>124400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>121100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>136500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>129200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>119800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>117600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>188100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>183300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>110600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>186300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>172000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>165400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>153000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>179400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>298200</v>
+      </c>
+      <c r="E44" s="3">
         <v>301900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>314700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>321400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>309400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>320100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>307600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>292100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>279500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>227800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>220200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>203300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>196200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>193400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>196000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>189400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>190400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>190600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>192100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>184900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>173400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>171000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>271000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>262900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>136200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>256800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>261700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>260700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>249700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>262900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>86500</v>
+      </c>
+      <c r="E45" s="3">
         <v>71900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>56300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>63700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>57000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>46100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>55100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>43600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>45800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>36300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>40600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>42800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>40200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>33400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>218600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>38000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>45200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>222000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>44100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>37000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>33300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>36200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E46" s="3">
         <v>594900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>614500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>679200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>679500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>664700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>634600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>648800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>636600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>515100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>492100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>463100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>452900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>421700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>431900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>461400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>477300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>409300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>430400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>430900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>469300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>741200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>604300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>608700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>585000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>571500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>540200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>516700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>494300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,192 +4100,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>687900</v>
+      </c>
+      <c r="E48" s="3">
         <v>681400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>698200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>705900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>701200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>690900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>716500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>741800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>786000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>627600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>646000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>539000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>555100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>541500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>532100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>532700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>549100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>535100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>554500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>557900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>556000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>497600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>844500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>870700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>515200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>856000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>838000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>804000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>775900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>771500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E49" s="3">
         <v>207000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>212500</v>
-      </c>
-      <c r="F49" s="3">
-        <v>213900</v>
       </c>
       <c r="G49" s="3">
         <v>213900</v>
       </c>
       <c r="H49" s="3">
+        <v>213900</v>
+      </c>
+      <c r="I49" s="3">
         <v>223200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>278400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>293800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>392500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>282300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>290500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>233500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>246200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>237000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>228700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>226700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>234600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>229200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>242000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>241800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>247100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>133300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>135200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>144100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>141600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>140700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>137300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>130000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>129400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E52" s="3">
         <v>49700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>51400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>52400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>52800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>56900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>67800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>64600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>65600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>32300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>34200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>23400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>71900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>69100</v>
-      </c>
-      <c r="V52" s="3">
-        <v>67300</v>
       </c>
       <c r="W52" s="3">
         <v>67300</v>
       </c>
       <c r="X52" s="3">
+        <v>67300</v>
+      </c>
+      <c r="Y52" s="3">
         <v>378700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>153100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>141000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>489000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>128600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>126300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>124100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>121700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>115200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1563800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1532900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1576600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1651500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1647400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1635800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1697300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1749000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1880600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1456600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1460100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1267900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1286900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1233900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1226900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1244200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1283800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1245600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1296000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1297900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1339800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1750800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1737100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1764600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1730800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1696800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1641800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1574800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1521300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1554200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>158500</v>
+      </c>
+      <c r="E57" s="3">
         <v>156900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>161100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>196400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>217600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>207700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>208200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>210500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>214000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>142600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>122800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>115500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>127500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>95500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>93600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>112900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>130000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>109600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>115200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>120000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>120700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>103400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>193100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>187700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>113200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>168800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>178800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>172300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>164300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>163700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E58" s="3">
         <v>7500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>51900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>48700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>51000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>49300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>39000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>35700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>25100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>22900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>25000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>22900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>22200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>23200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>19900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>10800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>11000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>11600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>11300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>10400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>9400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E59" s="3">
         <v>91200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>91500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>99300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>90900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>99700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>86600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>106700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>107900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>93000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>84600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>80800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>78800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>78000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>77500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>85600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>86700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>81800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>101300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>216100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>132800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>139400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>222700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>156000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>150600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>139100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>149700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>141000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>280400</v>
+      </c>
+      <c r="E60" s="3">
         <v>255600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>262900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>307900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>360400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>356000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>327500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>368200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>371200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>274700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>242400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>235700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>233300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>198200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>194500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>211800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>230500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>217400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>225100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>221600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>232800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>330400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>336900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>338700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>347200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>336000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>339800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>320800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>323000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>316100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>853200</v>
+      </c>
+      <c r="E61" s="3">
         <v>847900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>853000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>852100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>793300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>770200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>779000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>758300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>738100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>423100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>445300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>271100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>288500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>308000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>324700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>325500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>336900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>329800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>361800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>370600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>401000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>635400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>510200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>494100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>470100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>459000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>431500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>400500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>363600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>367500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>173400</v>
+      </c>
+      <c r="E62" s="3">
         <v>175800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>181800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>178900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>175700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>189900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>200800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>205900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>228600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>195500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>201200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>190000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>187100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>169400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>166700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>163900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>160400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>159600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>165900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>169500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>167100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>178000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>203100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>207800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>204600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>191200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>185500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>184700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>180800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>178900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1306900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1279200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1297700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1338900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1329300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1316100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1307400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1332300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1337800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>893200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>888800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>696800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>708900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>675500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>685900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>701300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>727800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>706800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>752900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>761700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>800900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1143800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1050100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1040600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1021900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>986200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>956700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>906000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>867400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>862600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>419800</v>
+      </c>
+      <c r="E72" s="3">
         <v>428500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>448300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>485300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>498900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>533200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>582700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>591000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>705600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>722200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>720900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>725800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>723400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>719600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>719000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>727400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>725800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>776400</v>
-      </c>
-      <c r="U72" s="3">
-        <v>769900</v>
       </c>
       <c r="V72" s="3">
         <v>769900</v>
       </c>
       <c r="W72" s="3">
+        <v>769900</v>
+      </c>
+      <c r="X72" s="3">
         <v>770300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>856100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>957600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>970700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>948400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>963900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>957400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>968800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>962900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>984500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>256900</v>
+      </c>
+      <c r="E76" s="3">
         <v>253700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>278800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>312600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>318000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>319700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>389900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>416700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>542800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>563300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>571200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>571100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>577900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>558400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>541000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>542900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>556000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>538800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>543100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>536200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>538900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>606900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>687000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>724000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>708900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>710600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>685000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>668800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>653800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>691700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-49500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-108300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-44900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-80100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-95800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E83" s="3">
         <v>15700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>15400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12700</v>
-      </c>
-      <c r="V83" s="3">
-        <v>12800</v>
       </c>
       <c r="W83" s="3">
         <v>12800</v>
       </c>
       <c r="X83" s="3">
+        <v>12800</v>
+      </c>
+      <c r="Y83" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>21400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>35000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>16100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E89" s="3">
         <v>10800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>23200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-66300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>36900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>83900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>25300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>86000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>29100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-34500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>337500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>51500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>24000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>28800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>56700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>4800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>21400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-71000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-303800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-176500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-187500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>21200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-36800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-36700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7903,13 +8136,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-6300</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>-6300</v>
       </c>
       <c r="J96" s="3">
-        <v>-6200</v>
+        <v>-6300</v>
       </c>
       <c r="K96" s="3">
         <v>-6200</v>
@@ -7918,7 +8151,7 @@
         <v>-6200</v>
       </c>
       <c r="M96" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="N96" s="3">
         <v>-6000</v>
@@ -7930,13 +8163,13 @@
         <v>-6000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-5800</v>
+        <v>-6000</v>
       </c>
       <c r="R96" s="3">
         <v>-5800</v>
       </c>
       <c r="S96" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="T96" s="3">
         <v>-5700</v>
@@ -7966,10 +8199,10 @@
         <v>-5700</v>
       </c>
       <c r="AC96" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-11100</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-5500</v>
       </c>
       <c r="AE96" s="3">
         <v>-5500</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>18500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>311100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>165000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-39300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-16300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-22300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-23600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-239700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>119500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>12900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>15800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>20200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>52500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>30500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-35600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>23500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-58600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>38000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-20700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>69200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-66000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-91400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>126900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>31900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>14000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-7800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>GLT</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>327300</v>
+      </c>
+      <c r="E8" s="3">
         <v>320400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>329900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>357000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>378200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>373900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>371800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>364000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>381700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>334500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>279700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>244900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>225700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>235300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>233500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>216200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>231600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>231000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>232500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>235100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>229100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>229500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>209900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>215700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>211200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>209300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>210100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>380900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>391800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>393000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>406600</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>292700</v>
+      </c>
+      <c r="E9" s="3">
         <v>289500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>285400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>338900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>342000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>331500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>334400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>326600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>350000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>302900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>241300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>209400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>186400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>194500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>195200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>184100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>194700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>194600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>194500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>197600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>193500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>198800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>180000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>182400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>174600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>171000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>172700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>313000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>671100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>336100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E10" s="3">
         <v>30900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>44500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>36200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>42400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>37400</v>
       </c>
       <c r="J10" s="3">
         <v>37400</v>
       </c>
       <c r="K10" s="3">
+        <v>37400</v>
+      </c>
+      <c r="L10" s="3">
         <v>31700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>39300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>40800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>32100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>36900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>36400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>38000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>37500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>35600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>30700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>29900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>33300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>36600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>38300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>37400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>67900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-279300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>56900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,37 +1318,40 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>17800</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>30700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>42500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>117300</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1348,8 +1368,8 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>328800</v>
+      </c>
+      <c r="E17" s="3">
         <v>316000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>327300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>367500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>372100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>396800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>405800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>355000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>497600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>345800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>265100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>236800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>208400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>221500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>219400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>207100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>219300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>217700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>218000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>219900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>217500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>227300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>205500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>208100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>203500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>200000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>199700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>367400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>371100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>422200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>381200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-22900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-34000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-115900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-29200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,242 +1781,249 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-76100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-400</v>
       </c>
       <c r="X20" s="3">
         <v>-400</v>
       </c>
       <c r="Y20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z20" s="3">
         <v>2400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E21" s="3">
         <v>18300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>18800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>25000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-98700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>22000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>30800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>25700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-50000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>26300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>14600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>35100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>36000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>52900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>42900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-13400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E22" s="3">
         <v>17500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>1800</v>
       </c>
       <c r="R22" s="3">
         <v>1800</v>
@@ -1992,7 +2032,7 @@
         <v>1800</v>
       </c>
       <c r="T22" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="U22" s="3">
         <v>1900</v>
@@ -2001,230 +2041,239 @@
         <v>1900</v>
       </c>
       <c r="W22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X22" s="3">
         <v>4700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>3900</v>
       </c>
       <c r="AG22" s="3">
         <v>3900</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-30200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-44300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-125100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-64600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>11900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-33400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-6600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-19900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-17200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-49100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-108200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-44800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>11600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-49100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-108200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-44800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,94 +2661,97 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E29" s="3">
         <v>-300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-2900</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>2500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>2600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>3600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-76900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-94500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>3300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>7100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>1800</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>76100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1400</v>
-      </c>
-      <c r="W32" s="3">
-        <v>400</v>
       </c>
       <c r="X32" s="3">
         <v>400</v>
       </c>
       <c r="Y32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-36900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-49500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-108300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-44900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-80100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-95800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-36900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-49500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-108300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-44900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-80100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-95800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E41" s="3">
         <v>50300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>53900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>88600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>110700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>95300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>80500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>138400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>87400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>99600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>59200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>104200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>58900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>76700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>142700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>234100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>107200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>117300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>116200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>84300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>69400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>57200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>55400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>50800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,388 +3718,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E43" s="3">
         <v>171000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>168400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>189600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>196900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>195700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>192400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>209500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>221200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>170200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>149000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>144200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>126500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>122800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>133600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>121700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>128700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>124400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>121100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>136500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>129200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>119800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>117600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>188100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>183300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>110600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>186300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>172000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>165400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>153000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>179400</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>299700</v>
+      </c>
+      <c r="E44" s="3">
         <v>298200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>301900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>314700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>321400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>309400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>320100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>307600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>292100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>279500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>227800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>220200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>203300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>196200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>193400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>196000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>189400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>190400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>190600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>192100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>184900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>173400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>171000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>271000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>262900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>136200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>256800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>261700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>260700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>249700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>262900</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E45" s="3">
         <v>86500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>71900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>72300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>63700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>57000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>46100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>45800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>37500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>36300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>40600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>40200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>33400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>218600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>38000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>45200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>222000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>44100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>37000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>33300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>36600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>584300</v>
+      </c>
+      <c r="E46" s="3">
         <v>606000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>594900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>614500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>679200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>679500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>664700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>634600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>648800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>636600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>515100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>492100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>463100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>452900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>421700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>431900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>461400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>477300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>409300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>430400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>430900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>469300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>741200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>604300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>608700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>585000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>571500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>540200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>516700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>494300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>674200</v>
+      </c>
+      <c r="E48" s="3">
         <v>687900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>681400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>698200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>705900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>701200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>690900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>716500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>741800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>786000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>627600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>646000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>539000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>555100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>541500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>532100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>532700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>549100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>535100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>554500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>557900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>556000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>497600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>844500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>870700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>515200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>856000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>838000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>804000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>775900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>771500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>204800</v>
+      </c>
+      <c r="E49" s="3">
         <v>214000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>207000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>212500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>213900</v>
       </c>
       <c r="H49" s="3">
         <v>213900</v>
       </c>
       <c r="I49" s="3">
+        <v>213900</v>
+      </c>
+      <c r="J49" s="3">
         <v>223200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>278400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>293800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>392500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>282300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>290500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>233500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>246200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>237000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>228700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>226700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>234600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>229200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>242000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>241800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>247100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>133300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>135200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>144100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>141600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>140700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>137300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>130000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>129400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E52" s="3">
         <v>55900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>49700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>51400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>52400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>52800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>56900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>67800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>64600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>65600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>33700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>34200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>23400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>22800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>71900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>69100</v>
-      </c>
-      <c r="W52" s="3">
-        <v>67300</v>
       </c>
       <c r="X52" s="3">
         <v>67300</v>
       </c>
       <c r="Y52" s="3">
+        <v>67300</v>
+      </c>
+      <c r="Z52" s="3">
         <v>378700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>153100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>141000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>489000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>128600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>126300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>124100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>121700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>115200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1517200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1563800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1532900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1576600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1651500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1647400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1635800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1697300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1749000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1880600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1456600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1460100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1267900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1286900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1233900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1226900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1244200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1283800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1245600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1296000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1297900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1339800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1750800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1737100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1764600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1730800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1696800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1641800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1574800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1521300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1554200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E57" s="3">
         <v>158500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>156900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>161100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>196400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>217600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>207700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>208200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>210500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>214000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>142600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>122800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>115500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>127500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>95500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>93600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>112900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>130000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>109600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>115200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>120000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>120700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>103400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>193100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>187700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>113200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>168800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>178800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>172300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>164300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>163700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E58" s="3">
         <v>7200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>51900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>48700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>49300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>39000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>36200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>35700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>25100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>23900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>22900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>25000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>22900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>22200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>23200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>19900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>11000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>11600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>11100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>9000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E59" s="3">
         <v>114800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>91200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>91500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>99300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>90900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>99700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>86600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>106700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>107900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>93000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>84600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>80800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>78800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>78000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>77500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>85600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>86700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>81800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>101300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>216100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>132800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>139400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>222700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>156000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>150600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>139100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>149700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>141000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>252600</v>
+      </c>
+      <c r="E60" s="3">
         <v>280400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>255600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>262900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>307900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>360400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>356000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>327500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>368200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>371200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>274700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>242400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>235700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>233300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>198200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>194500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>211800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>230500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>217400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>225100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>221600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>232800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>330400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>336900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>338700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>347200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>336000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>339800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>320800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>323000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>316100</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>868200</v>
+      </c>
+      <c r="E61" s="3">
         <v>853200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>847900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>853000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>852100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>793300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>770200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>779000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>758300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>738100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>423100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>445300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>271100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>288500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>308000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>324700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>325500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>336900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>329800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>361800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>370600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>401000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>635400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>510200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>494100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>470100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>459000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>431500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>400500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>363600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>367500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>173100</v>
+      </c>
+      <c r="E62" s="3">
         <v>173400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>175800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>181800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>178900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>175700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>189900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>200800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>205900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>228600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>195500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>201200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>190000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>187100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>169400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>166700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>163900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>160400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>159600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>165900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>169500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>167100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>178000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>203100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>207800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>204600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>191200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>185500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>184700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>180800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>178900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1293900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1306900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1279200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1297700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1338900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1329300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1316100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1307400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1332300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1337800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>893200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>888800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>696800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>708900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>675500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>685900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>701300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>727800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>706800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>752900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>761700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>800900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1143800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1050100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1040600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1021900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>986200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>956700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>906000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>867400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>862600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>393500</v>
+      </c>
+      <c r="E72" s="3">
         <v>419800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>428500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>448300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>485300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>498900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>533200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>582700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>591000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>705600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>722200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>720900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>725800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>723400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>719600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>719000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>727400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>725800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>776400</v>
-      </c>
-      <c r="V72" s="3">
-        <v>769900</v>
       </c>
       <c r="W72" s="3">
         <v>769900</v>
       </c>
       <c r="X72" s="3">
+        <v>769900</v>
+      </c>
+      <c r="Y72" s="3">
         <v>770300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>856100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>957600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>970700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>948400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>963900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>957400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>968800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>962900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>984500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>223300</v>
+      </c>
+      <c r="E76" s="3">
         <v>256900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>253700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>278800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>312600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>318000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>319700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>389900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>416700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>542800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>563300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>571200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>571100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>577900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>558400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>541000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>542900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>556000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>538800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>543100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>536200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>538900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>606900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>687000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>724000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>708900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>710600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>685000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>668800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>653800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>691700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-36900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-49500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-108300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-44900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-80100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-95800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E83" s="3">
         <v>15900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12700</v>
-      </c>
-      <c r="W83" s="3">
-        <v>12800</v>
       </c>
       <c r="X83" s="3">
         <v>12800</v>
       </c>
       <c r="Y83" s="3">
+        <v>12800</v>
+      </c>
+      <c r="Z83" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>21400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>35000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>17300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>16100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E89" s="3">
         <v>15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-66300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>36900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>83900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>25300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>86000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>29100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-34500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>337500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>51500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>24000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>28800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>56700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>4800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>21400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-71000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-36600</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-303800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-176500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-187500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>4500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>21200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-31100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-36800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-36700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8139,13 +8373,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-6300</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>-6300</v>
       </c>
       <c r="K96" s="3">
-        <v>-6200</v>
+        <v>-6300</v>
       </c>
       <c r="L96" s="3">
         <v>-6200</v>
@@ -8154,7 +8388,7 @@
         <v>-6200</v>
       </c>
       <c r="N96" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="O96" s="3">
         <v>-6000</v>
@@ -8166,13 +8400,13 @@
         <v>-6000</v>
       </c>
       <c r="R96" s="3">
-        <v>-5800</v>
+        <v>-6000</v>
       </c>
       <c r="S96" s="3">
         <v>-5800</v>
       </c>
       <c r="T96" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="U96" s="3">
         <v>-5700</v>
@@ -8202,10 +8436,10 @@
         <v>-5700</v>
       </c>
       <c r="AD96" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-11100</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-5500</v>
       </c>
       <c r="AF96" s="3">
         <v>-5500</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>15200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>18500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>311100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>165000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-37800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-22300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-239700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>119500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>12900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>15800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>20200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>52500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>30500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-35600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>23500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-58600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>38000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>39800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-15900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>69200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-17700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-66000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-91400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>126900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>31900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>14800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-7800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>GLT</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>329400</v>
+      </c>
+      <c r="E8" s="3">
         <v>327300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>320400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>329900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>357000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>378200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>373900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>371800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>364000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>381700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>334500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>279700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>244900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>225700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>235300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>233500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>216200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>231600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>231000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>232500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>235100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>229100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>229500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>209900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>215700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>211200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>209300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>210100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>380900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>391800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>393000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>406600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -902,195 +909,201 @@
         <v>292700</v>
       </c>
       <c r="E9" s="3">
+        <v>292700</v>
+      </c>
+      <c r="F9" s="3">
         <v>289500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>285400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>338900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>342000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>331500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>334400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>326600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>350000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>302900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>241300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>209400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>186400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>194500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>195200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>184100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>194700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>194600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>194500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>197600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>193500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>198800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>180000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>182400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>174600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>171000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>172700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>313000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>671100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>336100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E10" s="3">
         <v>34600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>18100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>36200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>42400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>37400</v>
       </c>
       <c r="K10" s="3">
         <v>37400</v>
       </c>
       <c r="L10" s="3">
+        <v>37400</v>
+      </c>
+      <c r="M10" s="3">
         <v>31700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>31600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>35500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>40800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>32100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>36900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>36400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>38000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>37500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>35600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>30700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>29900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>33300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>36600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>38300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>37400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>67900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-279300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>56900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>61100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,40 +1338,43 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17800</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>30700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>42500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>117300</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1371,8 +1391,8 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>322100</v>
+      </c>
+      <c r="E17" s="3">
         <v>328800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>316000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>327300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>367500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>372100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>396800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>405800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>355000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>497600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>345800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>265100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>236800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>208400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>221500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>219400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>207100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>219300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>217700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>218000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>219900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>217500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>227300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>205500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>208100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>203500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>200000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>199700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>367400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>371100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>422200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>381200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-22900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-34000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-115900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>13500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-29200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>25400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,251 +1815,258 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-76100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-400</v>
       </c>
       <c r="Y20" s="3">
         <v>-400</v>
       </c>
       <c r="Z20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA20" s="3">
         <v>2400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E21" s="3">
         <v>12400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>25000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-98700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>30800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>25700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>16200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>27200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-50000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>26500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>24000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>14600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>35100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>36000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>52900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>42900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-13400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>41200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E22" s="3">
         <v>17700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1800</v>
       </c>
       <c r="S22" s="3">
         <v>1800</v>
@@ -2035,7 +2075,7 @@
         <v>1800</v>
       </c>
       <c r="U22" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="V22" s="3">
         <v>1900</v>
@@ -2044,236 +2084,245 @@
         <v>1900</v>
       </c>
       <c r="X22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>4700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>3900</v>
       </c>
       <c r="AH22" s="3">
         <v>3900</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-44300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-125100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-64600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>11800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>11900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-33400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-19900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-17200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-49100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-108200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-44800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>11600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-49100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-108200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-44800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>11600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2673,88 +2734,88 @@
         <v>-500</v>
       </c>
       <c r="E29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F29" s="3">
         <v>-300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-2900</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>2500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>2600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>3600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-76900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-94500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>3300</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>7100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>1800</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>76100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>400</v>
       </c>
       <c r="Y32" s="3">
         <v>400</v>
       </c>
       <c r="Z32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-26300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-49500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-108300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-44900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-80100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-95800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>11600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-26300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-49500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-108300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-44900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-80100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-95800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>11600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E41" s="3">
         <v>30200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>53900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>88600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>110700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>95300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>71500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>80500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>138400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>87400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>99600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>59200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>104200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>126200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>57000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>58900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>76700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>142700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>234100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>107200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>117300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>116200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>84300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>69400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>57200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>55400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>50800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E43" s="3">
         <v>180500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>171000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>168400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>189600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>196900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>195700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>192400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>209500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>221200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>170200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>149000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>144200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>126500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>122800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>133600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>121700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>128700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>124400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>121100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>136500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>129200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>119800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>117600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>188100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>183300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>110600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>186300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>172000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>165400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>153000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>179400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>305100</v>
+      </c>
+      <c r="E44" s="3">
         <v>299700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>298200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>301900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>314700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>321400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>309400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>320100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>307600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>292100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>279500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>227800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>220200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>203300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>196200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>193400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>196000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>189400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>190400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>190600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>192100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>184900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>173400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>171000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>271000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>262900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>136200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>256800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>261700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>260700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>249700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>262900</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E45" s="3">
         <v>73900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>86500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>71900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>72300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>63700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>57000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>46100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>55100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>48400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>43600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>45800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>35500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>37500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>36300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>40600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>42800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>33400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>218600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>38000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>45200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>222000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>44100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>37000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>33300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>36200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>36600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>586200</v>
+      </c>
+      <c r="E46" s="3">
         <v>584300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>606000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>594900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>614500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>679200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>679500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>664700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>634600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>648800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>636600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>515100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>492100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>463100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>452900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>421700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>431900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>461400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>477300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>409300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>430400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>430900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>469300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>741200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>604300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>608700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>585000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>571500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>540200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>516700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>494300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>638500</v>
+      </c>
+      <c r="E48" s="3">
         <v>674200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>687900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>681400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>698200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>705900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>701200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>690900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>716500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>741800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>786000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>627600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>646000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>539000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>555100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>541500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>532100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>532700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>549100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>535100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>554500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>557900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>556000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>497600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>844500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>870700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>515200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>856000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>838000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>804000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>775900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>771500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>201700</v>
+      </c>
+      <c r="E49" s="3">
         <v>204800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>214000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>207000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>212500</v>
-      </c>
-      <c r="H49" s="3">
-        <v>213900</v>
       </c>
       <c r="I49" s="3">
         <v>213900</v>
       </c>
       <c r="J49" s="3">
+        <v>213900</v>
+      </c>
+      <c r="K49" s="3">
         <v>223200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>278400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>293800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>392500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>282300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>290500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>233500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>246200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>237000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>228700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>226700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>234600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>229200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>242000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>241800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>247100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>133300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>135200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>144100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>141600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>140700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>137300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>130000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>129400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>138000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E52" s="3">
         <v>54000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>49700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>51400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>52400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>52800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>56900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>67800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>64600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>65600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>32700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>33700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>34200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>23400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>22800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>71900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>69100</v>
-      </c>
-      <c r="X52" s="3">
-        <v>67300</v>
       </c>
       <c r="Y52" s="3">
         <v>67300</v>
       </c>
       <c r="Z52" s="3">
+        <v>67300</v>
+      </c>
+      <c r="AA52" s="3">
         <v>378700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>153100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>141000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>489000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>128600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>126300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>124100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>121700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>115200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1505000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1517200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1563800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1532900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1576600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1651500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1647400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1635800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1697300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1749000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1880600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1456600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1460100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1267900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1286900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1233900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1226900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1244200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1283800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1245600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1296000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1297900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1339800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1750800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1737100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1764600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1730800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1696800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1641800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1574800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1521300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1554200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>156500</v>
+      </c>
+      <c r="E57" s="3">
         <v>134200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>158500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>156900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>161100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>196400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>217600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>207700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>208200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>210500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>214000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>142600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>122800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>115500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>127500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>95500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>93600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>112900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>130000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>109600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>115200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>120000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>120700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>103400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>193100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>187700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>113200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>168800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>178800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>172300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>164300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>163700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E58" s="3">
         <v>7500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>51900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>32700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>51000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>49300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>39000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>36200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>35700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>25100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>23900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>22900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>25000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>22900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>22200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>23200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>11000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>11300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>10400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>9400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E59" s="3">
         <v>110900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>114800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>91200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>91500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>99300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>90900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>99700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>86600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>106700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>107900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>93000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>83400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>84600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>80800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>78800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>78000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>77500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>85600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>86700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>81800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>101300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>216100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>132800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>139400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>222700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>156000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>150600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>139100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>149700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>141000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>265300</v>
+      </c>
+      <c r="E60" s="3">
         <v>252600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>280400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>255600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>262900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>307900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>360400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>356000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>327500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>368200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>371200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>274700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>242400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>235700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>233300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>198200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>194500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>211800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>230500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>217400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>225100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>221600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>232800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>330400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>336900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>338700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>347200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>336000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>339800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>320800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>323000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>316100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>861900</v>
+      </c>
+      <c r="E61" s="3">
         <v>868200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>853200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>847900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>853000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>852100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>793300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>770200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>779000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>758300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>738100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>423100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>445300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>271100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>288500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>308000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>324700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>325500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>336900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>329800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>361800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>370600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>401000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>635400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>510200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>494100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>470100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>459000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>431500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>400500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>363600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>367500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>172300</v>
+      </c>
+      <c r="E62" s="3">
         <v>173100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>173400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>175800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>181800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>178900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>175700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>189900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>200800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>205900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>228600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>195500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>201200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>190000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>187100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>169400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>166700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>163900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>160400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>159600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>165900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>169500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>167100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>178000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>203100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>207800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>204600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>191200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>185500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>184700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>180800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>178900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1299500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1293900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1306900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1279200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1297700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1338900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1329300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1316100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1307400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1332300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1337800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>893200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>888800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>696800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>708900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>675500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>685900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>701300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>727800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>706800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>752900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>761700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>800900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1143800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1050100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1040600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1021900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>986200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>956700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>906000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>867400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>862600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>377200</v>
+      </c>
+      <c r="E72" s="3">
         <v>393500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>419800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>428500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>448300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>485300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>498900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>533200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>582700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>591000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>705600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>722200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>720900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>725800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>723400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>719600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>719000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>727400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>725800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>776400</v>
-      </c>
-      <c r="W72" s="3">
-        <v>769900</v>
       </c>
       <c r="X72" s="3">
         <v>769900</v>
       </c>
       <c r="Y72" s="3">
+        <v>769900</v>
+      </c>
+      <c r="Z72" s="3">
         <v>770300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>856100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>957600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>970700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>948400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>963900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>957400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>968800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>962900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>984500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>205500</v>
+      </c>
+      <c r="E76" s="3">
         <v>223300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>256900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>253700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>278800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>312600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>318000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>319700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>389900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>416700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>542800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>563300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>571200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>571100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>577900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>558400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>541000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>542900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>556000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>538800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>543100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>536200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>538900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>606900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>687000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>724000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>708900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>710600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>685000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>668800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>653800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>691700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-26300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-49500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-108300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-44900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-80100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-95800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>11600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E83" s="3">
         <v>15800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>15400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12700</v>
-      </c>
-      <c r="X83" s="3">
-        <v>12800</v>
       </c>
       <c r="Y83" s="3">
         <v>12800</v>
       </c>
       <c r="Z83" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AA83" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>21400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>35000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>17300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>16100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-33600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-66300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>36900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>83900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>25300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>86000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>29100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>337500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>51500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>24000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>28800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>56700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>4800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>21400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-71000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-36600</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-303800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-176500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-187500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>4500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>21200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-31100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-36800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-36700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8376,13 +8610,13 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-6300</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-6300</v>
       </c>
       <c r="L96" s="3">
-        <v>-6200</v>
+        <v>-6300</v>
       </c>
       <c r="M96" s="3">
         <v>-6200</v>
@@ -8391,7 +8625,7 @@
         <v>-6200</v>
       </c>
       <c r="O96" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="P96" s="3">
         <v>-6000</v>
@@ -8403,13 +8637,13 @@
         <v>-6000</v>
       </c>
       <c r="S96" s="3">
-        <v>-5800</v>
+        <v>-6000</v>
       </c>
       <c r="T96" s="3">
         <v>-5800</v>
       </c>
       <c r="U96" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="V96" s="3">
         <v>-5700</v>
@@ -8439,10 +8673,10 @@
         <v>-5700</v>
       </c>
       <c r="AE96" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-11100</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-5500</v>
       </c>
       <c r="AG96" s="3">
         <v>-5500</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E100" s="3">
         <v>20800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>15200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>311100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>165000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-39300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-37800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-22300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-23600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-239700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>119500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>12900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>15800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>20200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>52500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>30500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-35600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>23500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-58600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>38000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>69200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-91400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>126900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>31900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>14000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-7800</v>
       </c>
     </row>
